--- a/KATALOG_DAMA.xlsx
+++ b/KATALOG_DAMA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B6586DB-2134-4DB5-BF19-F740E38E0507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D764C424-B331-4193-BF47-651B11AF5920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3270" yWindow="2535" windowWidth="15375" windowHeight="7875" xr2:uid="{18B9A474-A199-46A4-8A04-E0A129F1C44E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{18B9A474-A199-46A4-8A04-E0A129F1C44E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="276">
   <si>
     <t>ALQURAN SAKU RESLETING QURAN MINI TERJEMAHAN | QURAN CANTIK | QURAN SAKU</t>
   </si>
@@ -850,6 +850,9 @@
   </si>
   <si>
     <t>A4 HVS</t>
+  </si>
+  <si>
+    <t>Alquran Terjemah Faheem A5 Kertas Koran | Alquran Wakaf Hadiah Hampers (BANDUNG)</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F8CC9F-DD7D-453D-93E0-632FA723DE62}">
-  <dimension ref="A1:F350"/>
+  <dimension ref="A1:F351"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.28515625" style="4" bestFit="1" customWidth="1"/>
@@ -6477,6 +6480,14 @@
         <v>75000</v>
       </c>
     </row>
+    <row r="351" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A351" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F351" s="5">
+        <v>16500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/KATALOG_DAMA.xlsx
+++ b/KATALOG_DAMA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D764C424-B331-4193-BF47-651B11AF5920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EE4429-AFCB-4889-B414-7F6451A3CD7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{18B9A474-A199-46A4-8A04-E0A129F1C44E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="280">
   <si>
     <t>ALQURAN SAKU RESLETING QURAN MINI TERJEMAHAN | QURAN CANTIK | QURAN SAKU</t>
   </si>
@@ -795,9 +795,6 @@
     <t>AL QURAN AL QUDDUS SAKU A7 KULIT RESLETING (BANDUNG)</t>
   </si>
   <si>
-    <t>AL QURAN CUSTOM NAMA FOTO DI COVER SISIPAN ACARA TASYAKUR TAHLIL YASIN (BANDUNG)</t>
-  </si>
-  <si>
     <t>Al Quran Al Quddus Tanpa terjemahan uk A5 DAN A4 Kertas HVS (BANDUNG)</t>
   </si>
   <si>
@@ -840,19 +837,34 @@
     <t>A7 HVS</t>
   </si>
   <si>
-    <t>AL FIKRAH</t>
-  </si>
-  <si>
-    <t>AL QUDDUS</t>
-  </si>
-  <si>
-    <t>AL AQEEL</t>
-  </si>
-  <si>
     <t>A4 HVS</t>
   </si>
   <si>
     <t>Alquran Terjemah Faheem A5 Kertas Koran | Alquran Wakaf Hadiah Hampers (BANDUNG)</t>
+  </si>
+  <si>
+    <t>AL QURAN CUSTOM NAMA FOTO SISIPAN COVER ACARA TASYAKUR TAHLIL YASIN (BANDUNG)</t>
+  </si>
+  <si>
+    <t>Custom cover</t>
+  </si>
+  <si>
+    <t>Custom sisipan+cover</t>
+  </si>
+  <si>
+    <t>Custom sisipan 2Lbr</t>
+  </si>
+  <si>
+    <t>Custom sisipan 1Lbr</t>
+  </si>
+  <si>
+    <t>A5 KORAN AL AQEEL</t>
+  </si>
+  <si>
+    <t>A5 HVS AL FIKRAH</t>
+  </si>
+  <si>
+    <t>A5 KORAN FAHEEM</t>
   </si>
 </sst>
 </file>
@@ -1282,7 +1294,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F8CC9F-DD7D-453D-93E0-632FA723DE62}">
-  <dimension ref="A1:F351"/>
+  <dimension ref="A1:F370"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.28515625" style="4" bestFit="1" customWidth="1"/>
@@ -6244,7 +6256,7 @@
         <v>251</v>
       </c>
       <c r="D328" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F328" s="5">
         <v>8500</v>
@@ -6255,7 +6267,7 @@
         <v>251</v>
       </c>
       <c r="D329" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F329" s="5">
         <v>21000</v>
@@ -6266,7 +6278,7 @@
         <v>251</v>
       </c>
       <c r="D330" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F330" s="5">
         <v>39000</v>
@@ -6277,7 +6289,7 @@
         <v>252</v>
       </c>
       <c r="D331" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F331" s="5">
         <v>14500</v>
@@ -6288,7 +6300,7 @@
         <v>252</v>
       </c>
       <c r="D332" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F332" s="5">
         <v>12500</v>
@@ -6299,7 +6311,7 @@
         <v>252</v>
       </c>
       <c r="D333" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F333" s="5">
         <v>21000</v>
@@ -6310,7 +6322,7 @@
         <v>252</v>
       </c>
       <c r="D334" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F334" s="5">
         <v>8500</v>
@@ -6342,149 +6354,415 @@
     </row>
     <row r="338" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A338" s="11" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="B338" t="s">
-        <v>271</v>
-      </c>
-      <c r="D338" t="s">
-        <v>269</v>
+        <v>279</v>
+      </c>
+      <c r="D338" s="2" t="s">
+        <v>276</v>
       </c>
       <c r="F338" s="5">
-        <v>26000</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="339" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A339" s="11" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="B339" t="s">
-        <v>272</v>
-      </c>
-      <c r="D339" t="s">
-        <v>269</v>
+        <v>279</v>
+      </c>
+      <c r="D339" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="F339" s="5">
-        <v>24000</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="340" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A340" s="11" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="B340" t="s">
-        <v>273</v>
-      </c>
-      <c r="D340" t="s">
-        <v>269</v>
+        <v>279</v>
+      </c>
+      <c r="D340" s="2" t="s">
+        <v>274</v>
       </c>
       <c r="F340" s="5">
-        <v>18000</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="341" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A341" s="11" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="B341" t="s">
-        <v>273</v>
-      </c>
-      <c r="D341" t="s">
-        <v>267</v>
+        <v>279</v>
+      </c>
+      <c r="D341" s="2" t="s">
+        <v>275</v>
       </c>
       <c r="F341" s="5">
-        <v>14500</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="342" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A342" s="11" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="B342" t="s">
+        <v>278</v>
+      </c>
+      <c r="D342" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F342" s="5">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A343" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B343" t="s">
+        <v>278</v>
+      </c>
+      <c r="D343" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D342" t="s">
-        <v>268</v>
-      </c>
-      <c r="F342" s="5">
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="343" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A343" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="D343" t="s">
-        <v>269</v>
-      </c>
       <c r="F343" s="5">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A344" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B344" t="s">
+        <v>278</v>
+      </c>
+      <c r="D344" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F344" s="5">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A345" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B345" t="s">
+        <v>278</v>
+      </c>
+      <c r="D345" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F345" s="5">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A346" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B346" t="s">
+        <v>9</v>
+      </c>
+      <c r="D346" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F346" s="5">
         <v>24000</v>
       </c>
     </row>
-    <row r="344" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A344" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="D344" t="s">
-        <v>274</v>
-      </c>
-      <c r="F344" s="5">
-        <v>39000</v>
-      </c>
-    </row>
-    <row r="345" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A345" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="F345" s="5">
-        <v>28000</v>
-      </c>
-    </row>
-    <row r="346" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A346" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="F346" s="5">
-        <v>26000</v>
-      </c>
-    </row>
-    <row r="347" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A347" s="11" t="s">
-        <v>260</v>
+        <v>272</v>
+      </c>
+      <c r="B347" t="s">
+        <v>9</v>
+      </c>
+      <c r="D347" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="F347" s="5">
-        <v>75000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="348" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A348" s="11" t="s">
-        <v>261</v>
+        <v>272</v>
+      </c>
+      <c r="B348" t="s">
+        <v>9</v>
+      </c>
+      <c r="D348" s="2" t="s">
+        <v>274</v>
       </c>
       <c r="F348" s="5">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="349" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A349" s="11" t="s">
-        <v>262</v>
+        <v>272</v>
+      </c>
+      <c r="B349" t="s">
+        <v>9</v>
+      </c>
+      <c r="D349" s="2" t="s">
+        <v>275</v>
       </c>
       <c r="F349" s="5">
-        <v>14000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="350" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A350" s="11" t="s">
-        <v>263</v>
+        <v>272</v>
+      </c>
+      <c r="B350" t="s">
+        <v>4</v>
+      </c>
+      <c r="D350" s="2" t="s">
+        <v>276</v>
       </c>
       <c r="F350" s="5">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A351" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B351" t="s">
+        <v>4</v>
+      </c>
+      <c r="D351" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F351" s="5">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A352" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B352" t="s">
+        <v>4</v>
+      </c>
+      <c r="D352" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F352" s="5">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A353" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B353" t="s">
+        <v>4</v>
+      </c>
+      <c r="D353" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F353" s="5">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A354" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B354" t="s">
+        <v>277</v>
+      </c>
+      <c r="D354" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F354" s="5">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A355" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B355" t="s">
+        <v>277</v>
+      </c>
+      <c r="D355" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F355" s="5">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A356" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B356" t="s">
+        <v>277</v>
+      </c>
+      <c r="D356" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F356" s="5">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A357" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B357" t="s">
+        <v>277</v>
+      </c>
+      <c r="D357" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F357" s="5">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A358" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B358" t="s">
+        <v>12</v>
+      </c>
+      <c r="D358" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F358" s="5">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A359" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B359" t="s">
+        <v>12</v>
+      </c>
+      <c r="D359" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F359" s="5">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A360" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B360" t="s">
+        <v>12</v>
+      </c>
+      <c r="D360" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F360" s="5">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A361" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B361" t="s">
+        <v>12</v>
+      </c>
+      <c r="D361" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F361" s="5">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A362" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="D362" t="s">
+        <v>268</v>
+      </c>
+      <c r="F362" s="5">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A363" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="D363" t="s">
+        <v>270</v>
+      </c>
+      <c r="F363" s="5">
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A364" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="F364" s="5">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A365" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="F365" s="5">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A366" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="F366" s="5">
         <v>75000</v>
       </c>
     </row>
-    <row r="351" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A351" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="F351" s="5">
+    <row r="367" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A367" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="F367" s="5">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A368" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="F368" s="5">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A369" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="F369" s="5">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A370" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="F370" s="5">
         <v>16500</v>
       </c>
     </row>
